--- a/reports/ibis_files/hibiki/hibiki.xlsx
+++ b/reports/ibis_files/hibiki/hibiki.xlsx
@@ -117,7 +117,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-09T23:35:19-05:00</t>
+          <t>2026-06-12T22:46:21-05:00</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IQ1</t>
+          <t>Below IQ1</t>
         </is>
       </c>
     </row>
@@ -257,7 +257,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7.2.1</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -267,8 +267,10 @@
           <t>Errors</t>
         </is>
       </c>
-      <c r="B16">
-        <v>0</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -277,8 +279,10 @@
           <t>Warnings</t>
         </is>
       </c>
-      <c r="B17">
-        <v>0</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -287,8 +291,10 @@
           <t>Cautions</t>
         </is>
       </c>
-      <c r="B18">
-        <v>0</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -299,7 +305,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C:\Users\simom\Desktop\Projects\IBIS_QA\ibischk721_win_64\ibischk7_64.exe</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -330,7 +336,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24">
@@ -350,7 +356,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -360,7 +366,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27">
@@ -370,7 +376,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28"/>
@@ -424,14 +430,14 @@
           <t>IBIS file passes IBISCHK</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="D31" t="inlineStr" s="5">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PASS=3. No existing '|IQ Score:' tag found inside the .ibs file. This is reported as a writeback note only; it does not fail the quality check because this tool is intended to help assign the score. | IBISCHK version not found documented inside the .ibs file. This is reported as a documentation note only; it does not block Level 1. | IBISCHK: 0 errors, 0 warning(s): IBISCHK path: C:\Users\simom\Desktop\Projects\IBIS_QA\ibischk721_win_64\ibischk7_64.exe</t>
+          <t>ERROR=1. Check module raised exception: TypeError: Path.read_text() got an unexpected keyword argument 'newline'</t>
         </is>
       </c>
     </row>
@@ -468,7 +474,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IQ3</t>
+          <t>Below IQ1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -520,7 +526,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IQ1</t>
+          <t>Below IQ1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -542,7 +548,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IQ1</t>
+          <t>Below IQ1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -564,7 +570,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IQ1</t>
+          <t>Below IQ1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -586,7 +592,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IQ1</t>
+          <t>Below IQ1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -813,7 +819,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IQ3</t>
+          <t>Below IQ1</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1241,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IQ1</t>
+          <t>Below IQ1</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2759,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IQ1</t>
+          <t>Below IQ1</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4277,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IQ1</t>
+          <t>Below IQ1</t>
         </is>
       </c>
     </row>
@@ -5789,7 +5795,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IQ1</t>
+          <t>Below IQ1</t>
         </is>
       </c>
     </row>
@@ -10918,7 +10924,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2.1-file-hibiki_iocl_i3c_i2c_ibis_20260211.ibs-1d9e589fd307</t>
+          <t>2.1-file-a11486_ibis-00001760_20260211_1855.ib-7e37f06b13df</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -10936,14 +10942,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E2" t="inlineStr" s="5">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr" s="5">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -10953,7 +10959,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>hibiki_iocl_i3c_i2c_ibis_20260211.ibs</t>
+          <t>a11486_ibis-00001760_20260211_1855.ibs</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -10973,7 +10979,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No existing '|IQ Score:' tag found inside the .ibs file. This is reported as a writeback note only; it does not fail the quality check because this tool is intended to help assign the score.</t>
+          <t>Check module raised exception: TypeError: Path.read_text() got an unexpected keyword argument 'newline'</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -10985,17 +10991,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2.1-file-hibiki_iocl_i3c_i2c_ibis_20260211.ibs-2a29472e1811</t>
+          <t>3.1.1-component-A11486_IBIS-00001760-2cfeb13a5054</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3.1.1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LEVEL 1</t>
+          <t>LEVEL 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -11003,24 +11009,24 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E3" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>component</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>hibiki_iocl_i3c_i2c_ibis_20260211.ibs</t>
+          <t>A11486_IBIS-00001760</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -11040,7 +11046,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>IBISCHK version not found documented inside the .ibs file. This is reported as a documentation note only; it does not block Level 1.</t>
+          <t>Bare-die component — stub package values expected, check NA</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -11052,17 +11058,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2.1-file-hibiki_iocl_i3c_i2c_ibis_20260211.ibs-0eefba1ffb2a</t>
+          <t>3.1.2-component-A11486_IBIS-00001760-84af4b1b361b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3.1.2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LEVEL 1</t>
+          <t>LEVEL 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -11070,24 +11076,24 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E4" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>component</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>hibiki_iocl_i3c_i2c_ibis_20260211.ibs</t>
+          <t>A11486_IBIS-00001760</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -11107,24 +11113,24 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>IBISCHK: 0 errors, 0 warning(s)</t>
+          <t>Bare-die component — package limits check NA</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>IBISCHK path: C:\Users\simom\Desktop\Projects\IBIS_QA\ibischk721_win_64\ibischk7_64.exe</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3.1.1-component-A11486_IBIS-00001760-c935e1701b21</t>
+          <t>3.2.1-component-A11486_IBIS-00001760-7b25be2a2f25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.1.1</t>
+          <t>3.2.1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -11134,17 +11140,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+          <t>semi_auto</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -11174,7 +11180,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Bare-die component — stub package values expected, check NA</t>
+          <t>[Pin] has 2 complete entry/entries with resolvable model references</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -11186,12 +11192,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3.1.2-component-A11486_IBIS-00001760-b47954054489</t>
+          <t>4.1-file-a11486_ibis-00001760_20260211_1855.ib-ad2e34de8fe5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.1.2</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -11201,27 +11207,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+          <t>semi_auto</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>file</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>A11486_IBIS-00001760</t>
+          <t>a11486_ibis-00001760_20260211_1855.ibs</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -11241,7 +11247,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Bare-die component — package limits check NA</t>
+          <t>[Model Selector] A11486_IBIS-00001760 has descriptions for 4 entry/entries</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -11253,32 +11259,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3.2.1-component-A11486_IBIS-00001760-38d6d8d36d36</t>
+          <t>3.2.2-component-A11486_IBIS-00001760-be443b26bdfc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3.2.1</t>
+          <t>3.2.2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LEVEL 2</t>
+          <t>LEVEL 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>semi_auto</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -11308,7 +11314,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>[Pin] has 2 complete entry/entries with resolvable model references</t>
+          <t>Bare-die component - per-pin package RLC completeness is not required</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -11320,12 +11326,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4.1-file-hibiki_iocl_i3c_i2c_ibis_20260211.ibs-6cbdfd211617</t>
+          <t>3.3.1-component-A11486_IBIS-00001760-5cb85f150fa3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.3.1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -11335,27 +11341,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>semi_auto</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>component</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>hibiki_iocl_i3c_i2c_ibis_20260211.ibs</t>
+          <t>A11486_IBIS-00001760</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -11375,7 +11381,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>[Model Selector] A11486_IBIS-00001760 has descriptions for 4 entry/entries</t>
+          <t>No [Diff Pin] section — check NA</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -11387,12 +11393,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3.2.2-component-A11486_IBIS-00001760-699d47b03fcd</t>
+          <t>3.3.2-component-A11486_IBIS-00001760-dcecfdafef1d</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.2.2</t>
+          <t>3.3.2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -11442,7 +11448,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Bare-die component - per-pin package RLC completeness is not required</t>
+          <t>No [Diff Pin] section — check NA</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -11454,12 +11460,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3.3.1-component-A11486_IBIS-00001760-0b07ba1e6d4b</t>
+          <t>5.1.1-model-I3C_RX_RPU0RPD0_rx-2f4efcad9644</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.3.1</t>
+          <t>5.1.1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -11469,27 +11475,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+          <t>semi_auto</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>model</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>A11486_IBIS-00001760</t>
+          <t>I3C_RX_RPU0RPD0_rx</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -11509,144 +11515,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No [Diff Pin] section — check NA</t>
+          <t>7 model parameter set(s) have typ/min/max order evidence</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>3.3.2-component-A11486_IBIS-00001760-bacefcac1569</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3.3.2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LEVEL 3</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>A11486_IBIS-00001760</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>No [Diff Pin] section — check NA</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>5.1.1-model-I3C_RX_RPU0RPD0_rx-0ab65cb33231</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>5.1.1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>semi_auto</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>I3C_RX_RPU0RPD0_rx</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>7 model parameter set(s) have typ/min/max order evidence</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
         <is>
           <t>C_comp
 Voltage Range
@@ -11658,15 +11530,149 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5.2.6-model-I3C_RX_RPU0RPD0_rx-8851f4affe9f</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>5.2.6</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>semi_auto</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>I3C_RX_RPU0RPD0_rx</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>No [Model Spec] S_Overshoot data parsed</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>5.2.8-model-I3C_RX_RPU0RPD0_rx-82b7b5cf48f4</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5.2.8</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>semi_auto</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>I3C_RX_RPU0RPD0_rx</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>No [Model Spec] D_Overshoot data parsed</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5.2.6-model-I3C_RX_RPU0RPD0_rx-a644db754c8f</t>
+          <t>5.5.2-model-I3C_RX_RPU0RPD0_rx-7ae338f52f55</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5.2.6</t>
+          <t>5.5.2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -11716,7 +11722,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No [Model Spec] S_Overshoot data parsed</t>
+          <t>No [Ramp] data parsed</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -11728,12 +11734,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5.2.8-model-I3C_RX_RPU0RPD0_rx-4c66409f821c</t>
+          <t>5.1.1-model-I2C_RX_RPU1RPD0_rx-cdc2b0f5c752</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5.2.8</t>
+          <t>5.1.1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -11746,14 +11752,14 @@
           <t>semi_auto</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+      <c r="E14" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -11763,7 +11769,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>I3C_RX_RPU0RPD0_rx</t>
+          <t>I2C_RX_RPU1RPD0_rx</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -11783,144 +11789,10 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No [Model Spec] D_Overshoot data parsed</t>
+          <t>7 model parameter set(s) have typ/min/max order evidence</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>5.5.2-model-I3C_RX_RPU0RPD0_rx-b031143ddedd</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>5.5.2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>semi_auto</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>I3C_RX_RPU0RPD0_rx</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>No [Ramp] data parsed</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>5.1.1-model-I2C_RX_RPU1RPD0_rx-51e35f0d4254</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>5.1.1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>semi_auto</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>I2C_RX_RPU1RPD0_rx</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>7 model parameter set(s) have typ/min/max order evidence</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
         <is>
           <t>C_comp
 Voltage Range
@@ -11932,15 +11804,149 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5.2.6-model-I2C_RX_RPU1RPD0_rx-8ae9f40e4dea</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5.2.6</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>semi_auto</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>I2C_RX_RPU1RPD0_rx</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>No [Model Spec] S_Overshoot data parsed</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>5.2.8-model-I2C_RX_RPU1RPD0_rx-f92e7ccdb0d2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5.2.8</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>semi_auto</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>I2C_RX_RPU1RPD0_rx</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>No [Model Spec] D_Overshoot data parsed</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5.2.6-model-I2C_RX_RPU1RPD0_rx-9aa20c8a7fef</t>
+          <t>5.5.2-model-I2C_RX_RPU1RPD0_rx-870f99c25736</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5.2.6</t>
+          <t>5.5.2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -11990,7 +11996,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No [Model Spec] S_Overshoot data parsed</t>
+          <t>No [Ramp] data parsed</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -12002,12 +12008,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5.2.8-model-I2C_RX_RPU1RPD0_rx-3816ad35ea77</t>
+          <t>5.1.1-model-I2C_TX_8mA_tx-44a9ef87686a</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5.2.8</t>
+          <t>5.1.1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -12020,14 +12026,14 @@
           <t>semi_auto</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+      <c r="E18" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -12037,7 +12043,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>I2C_RX_RPU1RPD0_rx</t>
+          <t>I2C_TX_8mA_tx</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12057,144 +12063,10 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No [Model Spec] D_Overshoot data parsed</t>
+          <t>7 model parameter set(s) have typ/min/max order evidence</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>5.5.2-model-I2C_RX_RPU1RPD0_rx-cd9574feb664</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>5.5.2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>semi_auto</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>I2C_RX_RPU1RPD0_rx</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>No [Ramp] data parsed</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>5.1.1-model-I2C_TX_8mA_tx-a121646ae597</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>5.1.1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>semi_auto</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>I2C_TX_8mA_tx</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>7 model parameter set(s) have typ/min/max order evidence</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
         <is>
           <t>C_comp
 Voltage Range
@@ -12206,15 +12078,149 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5.2.6-model-I2C_TX_8mA_tx-af1f74031ed5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5.2.6</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>semi_auto</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>I2C_TX_8mA_tx</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>No complete S_Overshoot typ/min/max values parsed</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5.2.8-model-I2C_TX_8mA_tx-ce0c17b23eb8</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5.2.8</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>semi_auto</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>I2C_TX_8mA_tx</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>No complete D_Overshoot typ/min/max values parsed</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5.2.6-model-I2C_TX_8mA_tx-b168dd2a9d86</t>
+          <t>5.5.2-model-I2C_TX_8mA_tx-e9c82ac69de2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5.2.6</t>
+          <t>5.5.2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -12227,14 +12233,14 @@
           <t>semi_auto</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+      <c r="E21" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -12264,24 +12270,25 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No complete S_Overshoot typ/min/max values parsed</t>
+          <t>Ramp typ/min/max slew order evidence is ordered</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t/>
+          <t>dV/dt_r
+dV/dt_f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5.2.8-model-I2C_TX_8mA_tx-1f13bc5369c1</t>
+          <t>5.1.1-model-I3C_TX_0p125mA_tx-d75ef599d7c7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5.2.8</t>
+          <t>5.1.1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -12294,14 +12301,14 @@
           <t>semi_auto</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+      <c r="E22" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -12311,7 +12318,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>I2C_TX_8mA_tx</t>
+          <t>I3C_TX_0p125mA_tx</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -12331,145 +12338,10 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No complete D_Overshoot typ/min/max values parsed</t>
+          <t>7 model parameter set(s) have typ/min/max order evidence</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>5.5.2-model-I2C_TX_8mA_tx-bde3b343407f</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>5.5.2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>semi_auto</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>I2C_TX_8mA_tx</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Ramp typ/min/max slew order evidence is ordered</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>dV/dt_r
-dV/dt_f</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>5.1.1-model-I3C_TX_0p125mA_tx-f75a831b19fc</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>5.1.1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>semi_auto</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>I3C_TX_0p125mA_tx</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>7 model parameter set(s) have typ/min/max order evidence</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
         <is>
           <t>C_comp
 Voltage Range
@@ -12481,15 +12353,149 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>5.2.6-model-I3C_TX_0p125mA_tx-084aae864ea2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5.2.6</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>semi_auto</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>I3C_TX_0p125mA_tx</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>No complete S_Overshoot typ/min/max values parsed</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>5.2.8-model-I3C_TX_0p125mA_tx-09f76ada0223</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>5.2.8</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>semi_auto</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>I3C_TX_0p125mA_tx</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>No complete D_Overshoot typ/min/max values parsed</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5.2.6-model-I3C_TX_0p125mA_tx-9351d7204171</t>
+          <t>5.5.2-model-I3C_TX_0p125mA_tx-d4efd8fa18e0</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5.2.6</t>
+          <t>5.5.2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -12502,14 +12508,14 @@
           <t>semi_auto</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+      <c r="E25" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12539,24 +12545,25 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No complete S_Overshoot typ/min/max values parsed</t>
+          <t>Ramp typ/min/max slew order evidence is ordered</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t/>
+          <t>dV/dt_r
+dV/dt_f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5.2.8-model-I3C_TX_0p125mA_tx-de5ac20557ce</t>
+          <t>5.1.2-model-I3C_RX_RPU0RPD0_rx-9f8e9b77613e</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5.2.8</t>
+          <t>5.1.2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -12569,14 +12576,14 @@
           <t>semi_auto</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+      <c r="E26" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12586,7 +12593,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>I3C_TX_0p125mA_tx</t>
+          <t>I3C_RX_RPU0RPD0_rx</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -12606,24 +12613,24 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No complete D_Overshoot typ/min/max values parsed</t>
+          <t>C_comp evidence is positive and within review threshold</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t/>
+          <t>C_comp</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5.5.2-model-I3C_TX_0p125mA_tx-0573cc1286c4</t>
+          <t>5.1.4-model-I3C_RX_RPU0RPD0_rx-87fced1b32aa</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5.5.2</t>
+          <t>5.1.4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -12653,7 +12660,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>I3C_TX_0p125mA_tx</t>
+          <t>I3C_RX_RPU0RPD0_rx</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -12673,145 +12680,10 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Ramp typ/min/max slew order evidence is ordered</t>
+          <t>Voltage/reference evidence parsed, defaults resolved, and basic consistency looks reasonable</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
-        <is>
-          <t>dV/dt_r
-dV/dt_f</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>5.1.2-model-I3C_RX_RPU0RPD0_rx-38b1a6a4b5cc</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>5.1.2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>semi_auto</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>I3C_RX_RPU0RPD0_rx</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>C_comp evidence is positive and within review threshold</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>C_comp</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>5.1.4-model-I3C_RX_RPU0RPD0_rx-b2ef9afd8a43</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>5.1.4</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>semi_auto</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>I3C_RX_RPU0RPD0_rx</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Voltage/reference evidence parsed, defaults resolved, and basic consistency looks reasonable</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
         <is>
           <t>Voltage Range: typ=1.2V, min=1.08V, max=1.32V (explicit)
 Pullup Reference: typ=1.2V, min=1.08V, max=1.32V (explicit)
@@ -12821,15 +12693,150 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>5.3.6-model-I3C_RX_RPU0RPD0_rx-9970343f1f00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5.3.6</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>semi_auto</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr" s="6">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr" s="6">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>I3C_RX_RPU0RPD0_rx</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>I-V stair-step evidence needs review</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>[GND Clamp]: roughness=0.262 &gt; 0.1
+[POWER Clamp]: roughness=0.2 &gt; 0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>5.3.14-model-I3C_RX_RPU0RPD0_rx-767f9dbd0524</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>5.3.14</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>semi_auto</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>I3C_RX_RPU0RPD0_rx</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>I-V point counts meet evidence threshold</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5.3.6-model-I3C_RX_RPU0RPD0_rx-e1a69e178b00</t>
+          <t>5.3.10-model-I3C_RX_RPU0RPD0_rx-5889540de971</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5.3.6</t>
+          <t>5.3.10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -12842,14 +12849,14 @@
           <t>semi_auto</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr" s="6">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr" s="6">
-        <is>
-          <t>WARN</t>
+      <c r="E30" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12864,7 +12871,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -12879,25 +12886,24 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>I-V stair-step evidence needs review</t>
+          <t>Clamp leakage evidence is within threshold at 0V</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>[GND Clamp]: roughness=0.262 &gt; 0.1
-[POWER Clamp]: roughness=0.2 &gt; 0.1</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5.3.14-model-I3C_RX_RPU0RPD0_rx-a0fa0bd207e4</t>
+          <t>5.4.1-model-I3C_RX_RPU0RPD0_rx-dab3e340c2e4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5.3.14</t>
+          <t>5.4.1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -12910,14 +12916,14 @@
           <t>semi_auto</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E31" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -12947,7 +12953,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>I-V point counts meet evidence threshold</t>
+          <t>No V-T waveform tables parsed</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -12959,12 +12965,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5.3.10-model-I3C_RX_RPU0RPD0_rx-c5035f3e7a84</t>
+          <t>5.4.2-model-I3C_RX_RPU0RPD0_rx-65080b13ca19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5.3.10</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -12977,14 +12983,14 @@
           <t>semi_auto</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E32" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13014,7 +13020,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Clamp leakage evidence is within threshold at 0V</t>
+          <t>No V-T waveform tables parsed</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -13026,17 +13032,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5.4.1-model-I3C_RX_RPU0RPD0_rx-c5b02eb2d512</t>
+          <t>5.4.3-model-I3C_RX_RPU0RPD0_rx-1af03d8eefe6</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5.4.1</t>
+          <t>5.4.3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LEVEL 2</t>
+          <t>LEVEL 3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -13093,12 +13099,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5.4.2-model-I3C_RX_RPU0RPD0_rx-4640dad9ff0e</t>
+          <t>5.4.4-model-I3C_RX_RPU0RPD0_rx-db4d5da88d83</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>5.4.4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -13160,17 +13166,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5.4.3-model-I3C_RX_RPU0RPD0_rx-e3a548ac537a</t>
+          <t>5.5.4-model-I3C_RX_RPU0RPD0_rx-e188a9e8f64e</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5.4.3</t>
+          <t>5.5.4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LEVEL 3</t>
+          <t>LEVEL 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -13215,7 +13221,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No V-T waveform tables parsed</t>
+          <t>Ramp or V-T waveform data absent</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -13227,17 +13233,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5.4.4-model-I3C_RX_RPU0RPD0_rx-0512e16b18dd</t>
+          <t>5.6.2-model-I3C_RX_RPU0RPD0_rx-27ea3a056f08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5.4.4</t>
+          <t>5.6.2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LEVEL 2</t>
+          <t>LEVEL 3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -13282,7 +13288,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No V-T waveform tables parsed</t>
+          <t>Model_type=Input does not require this Vref consistency evidence</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -13294,12 +13300,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5.5.4-model-I3C_RX_RPU0RPD0_rx-329e933165be</t>
+          <t>5.1.2-model-I2C_RX_RPU1RPD0_rx-5600159649ad</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5.5.4</t>
+          <t>5.1.2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -13312,14 +13318,14 @@
           <t>semi_auto</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+      <c r="E37" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -13329,7 +13335,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>I3C_RX_RPU0RPD0_rx</t>
+          <t>I2C_RX_RPU1RPD0_rx</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -13349,29 +13355,29 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Ramp or V-T waveform data absent</t>
+          <t>C_comp evidence is positive and within review threshold</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t/>
+          <t>C_comp</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5.6.2-model-I3C_RX_RPU0RPD0_rx-3d7256d45ea3</t>
+          <t>5.1.4-model-I2C_RX_RPU1RPD0_rx-1c392b74fbf9</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5.6.2</t>
+          <t>5.1.4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LEVEL 3</t>
+          <t>LEVEL 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -13379,14 +13385,14 @@
           <t>semi_auto</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+      <c r="E38" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -13396,7 +13402,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>I3C_RX_RPU0RPD0_rx</t>
+          <t>I2C_RX_RPU1RPD0_rx</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -13416,144 +13422,10 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Model_type=Input does not require this Vref consistency evidence</t>
+          <t>Voltage/reference evidence parsed, defaults resolved, and basic consistency looks reasonable</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>5.1.2-model-I2C_RX_RPU1RPD0_rx-73fa12e63941</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>5.1.2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>semi_auto</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>I2C_RX_RPU1RPD0_rx</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>C_comp evidence is positive and within review threshold</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>C_comp</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>5.1.4-model-I2C_RX_RPU1RPD0_rx-5b512b75e2c8</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>5.1.4</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>semi_auto</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>I2C_RX_RPU1RPD0_rx</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Voltage/reference evidence parsed, defaults resolved, and basic consistency looks reasonable</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
         <is>
           <t>Voltage Range: typ=1.2V, min=1.08V, max=1.32V (explicit)
 Pullup Reference: typ=1.2V, min=1.08V, max=1.32V (explicit)
@@ -13563,15 +13435,150 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>5.3.6-model-I2C_RX_RPU1RPD0_rx-e4c567ad8626</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>5.3.6</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>semi_auto</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr" s="6">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr" s="6">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>I2C_RX_RPU1RPD0_rx</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>I-V stair-step evidence needs review</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>[GND Clamp]: roughness=0.262 &gt; 0.1
+[POWER Clamp]: roughness=0.2 &gt; 0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>5.3.14-model-I2C_RX_RPU1RPD0_rx-12d7e9f7afa6</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>5.3.14</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>semi_auto</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>I2C_RX_RPU1RPD0_rx</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>I-V point counts meet evidence threshold</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5.3.6-model-I2C_RX_RPU1RPD0_rx-090fb0498636</t>
+          <t>5.3.10-model-I2C_RX_RPU1RPD0_rx-fd83bb241c61</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5.3.6</t>
+          <t>5.3.10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -13621,25 +13628,24 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>I-V stair-step evidence needs review</t>
+          <t>Clamp leakage evidence needs review</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>[GND Clamp]: roughness=0.262 &gt; 0.1
-[POWER Clamp]: roughness=0.2 &gt; 0.1</t>
+          <t>[GND Clamp]: I(0V)=-17.8 uA</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5.3.14-model-I2C_RX_RPU1RPD0_rx-24d4bffb16ba</t>
+          <t>5.4.1-model-I2C_RX_RPU1RPD0_rx-7cb103e17947</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5.3.14</t>
+          <t>5.4.1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -13652,14 +13658,14 @@
           <t>semi_auto</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E42" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -13689,7 +13695,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>I-V point counts meet evidence threshold</t>
+          <t>No V-T waveform tables parsed</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -13701,12 +13707,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5.3.10-model-I2C_RX_RPU1RPD0_rx-209f569ca416</t>
+          <t>5.4.2-model-I2C_RX_RPU1RPD0_rx-db94f07d2ab6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5.3.10</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -13719,14 +13725,14 @@
           <t>semi_auto</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr" s="6">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr" s="6">
-        <is>
-          <t>WARN</t>
+      <c r="E43" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -13741,7 +13747,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -13756,29 +13762,29 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Clamp leakage evidence needs review</t>
+          <t>No V-T waveform tables parsed</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>[GND Clamp]: I(0V)=-17.8 uA</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5.4.1-model-I2C_RX_RPU1RPD0_rx-b286caa63072</t>
+          <t>5.4.3-model-I2C_RX_RPU1RPD0_rx-6a0f00e89f0c</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5.4.1</t>
+          <t>5.4.3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LEVEL 2</t>
+          <t>LEVEL 3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -13835,12 +13841,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5.4.2-model-I2C_RX_RPU1RPD0_rx-747e27fc05ed</t>
+          <t>5.4.4-model-I2C_RX_RPU1RPD0_rx-f461beb865a2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>5.4.4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -13902,17 +13908,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5.4.3-model-I2C_RX_RPU1RPD0_rx-b121674a6168</t>
+          <t>5.5.4-model-I2C_RX_RPU1RPD0_rx-f81af41057a8</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5.4.3</t>
+          <t>5.5.4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LEVEL 3</t>
+          <t>LEVEL 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -13957,7 +13963,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No V-T waveform tables parsed</t>
+          <t>Ramp or V-T waveform data absent</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -13969,17 +13975,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5.4.4-model-I2C_RX_RPU1RPD0_rx-f2fc764bfb26</t>
+          <t>5.6.2-model-I2C_RX_RPU1RPD0_rx-f48c0f6341d4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5.4.4</t>
+          <t>5.6.2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LEVEL 2</t>
+          <t>LEVEL 3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -14024,7 +14030,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No V-T waveform tables parsed</t>
+          <t>Model_type=Input does not require this Vref consistency evidence</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -14036,12 +14042,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5.5.4-model-I2C_RX_RPU1RPD0_rx-87d9341f1ef7</t>
+          <t>5.1.2-model-I2C_TX_8mA_tx-5ed70019043c</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5.5.4</t>
+          <t>5.1.2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -14054,14 +14060,14 @@
           <t>semi_auto</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+      <c r="E48" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -14071,7 +14077,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>I2C_RX_RPU1RPD0_rx</t>
+          <t>I2C_TX_8mA_tx</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -14091,29 +14097,29 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Ramp or V-T waveform data absent</t>
+          <t>C_comp evidence is positive and within review threshold</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t/>
+          <t>C_comp</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5.6.2-model-I2C_RX_RPU1RPD0_rx-4d95eec58df1</t>
+          <t>5.1.4-model-I2C_TX_8mA_tx-4eaa766bb64d</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5.6.2</t>
+          <t>5.1.4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LEVEL 3</t>
+          <t>LEVEL 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -14121,14 +14127,14 @@
           <t>semi_auto</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+      <c r="E49" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -14138,7 +14144,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>I2C_RX_RPU1RPD0_rx</t>
+          <t>I2C_TX_8mA_tx</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -14158,144 +14164,10 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Model_type=Input does not require this Vref consistency evidence</t>
+          <t>Voltage/reference evidence parsed, defaults resolved, and basic consistency looks reasonable</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>5.1.2-model-I2C_TX_8mA_tx-f5a890502f70</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>5.1.2</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>semi_auto</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>I2C_TX_8mA_tx</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>C_comp evidence is positive and within review threshold</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>C_comp</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>5.1.4-model-I2C_TX_8mA_tx-30c58516bfa3</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>5.1.4</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>semi_auto</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>I2C_TX_8mA_tx</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Voltage/reference evidence parsed, defaults resolved, and basic consistency looks reasonable</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
         <is>
           <t>Voltage Range: typ=1.2V, min=1.08V, max=1.32V (explicit)
 Pullup Reference: typ=1.2V, min=1.08V, max=1.32V (explicit)
@@ -14305,15 +14177,150 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>5.3.6-model-I2C_TX_8mA_tx-b8991f5c0225</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>5.3.6</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>semi_auto</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr" s="6">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr" s="6">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>I2C_TX_8mA_tx</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>I-V stair-step evidence needs review</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>[GND Clamp]: roughness=0.262 &gt; 0.1
+[POWER Clamp]: roughness=0.2 &gt; 0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>5.3.14-model-I2C_TX_8mA_tx-37bd04b31122</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>5.3.14</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>semi_auto</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>I2C_TX_8mA_tx</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>I-V point counts meet evidence threshold</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5.3.6-model-I2C_TX_8mA_tx-1e6fc1e9c917</t>
+          <t>5.3.10-model-I2C_TX_8mA_tx-357b84725bdd</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5.3.6</t>
+          <t>5.3.10</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -14326,14 +14333,14 @@
           <t>semi_auto</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr" s="6">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr" s="6">
-        <is>
-          <t>WARN</t>
+      <c r="E52" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -14348,7 +14355,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -14363,25 +14370,24 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>I-V stair-step evidence needs review</t>
+          <t>Clamp leakage evidence is within threshold at 0V</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>[GND Clamp]: roughness=0.262 &gt; 0.1
-[POWER Clamp]: roughness=0.2 &gt; 0.1</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5.3.14-model-I2C_TX_8mA_tx-374130fc932e</t>
+          <t>5.4.1-model-I2C_TX_8mA_tx-b5224b5d8a8b</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5.3.14</t>
+          <t>5.4.1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -14431,7 +14437,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>I-V point counts meet evidence threshold</t>
+          <t>V-T waveform evidence includes 2 rising and 2 falling table(s)</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -14443,12 +14449,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5.3.10-model-I2C_TX_8mA_tx-f99c54a0c8c7</t>
+          <t>5.4.2-model-I2C_TX_8mA_tx-5f505b5854b6</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5.3.10</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -14498,7 +14504,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Clamp leakage evidence is within threshold at 0V</t>
+          <t>V-T point counts meet evidence threshold</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -14510,17 +14516,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5.4.1-model-I2C_TX_8mA_tx-7ce9e98d0780</t>
+          <t>5.4.3-model-I2C_TX_8mA_tx-564d0a06de2f</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5.4.1</t>
+          <t>5.4.3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LEVEL 2</t>
+          <t>LEVEL 3</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -14565,7 +14571,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>V-T waveform evidence includes 2 rising and 2 falling table(s)</t>
+          <t>V-T duration evidence is within threshold</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -14577,12 +14583,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5.4.2-model-I2C_TX_8mA_tx-a74a8986b136</t>
+          <t>5.4.4-model-I2C_TX_8mA_tx-8f91347c98e1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>5.4.4</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -14632,7 +14638,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>V-T point counts meet evidence threshold</t>
+          <t>V-T endpoint fixture evidence is within threshold</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -14644,17 +14650,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5.4.3-model-I2C_TX_8mA_tx-cb0c3df0eed3</t>
+          <t>5.5.4-model-I2C_TX_8mA_tx-fa90b9d7b1a8</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5.4.3</t>
+          <t>5.5.4</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LEVEL 3</t>
+          <t>LEVEL 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -14699,29 +14705,29 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>V-T duration evidence is within threshold</t>
+          <t>Ramp dt evidence is near V-T 20-80% crossing span</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t/>
+          <t>avg Ramp dt=1.644e-10s, avg V-T 20-80% span=1.581e-10s, diff=4.0%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5.4.4-model-I2C_TX_8mA_tx-b7015aa9dcfc</t>
+          <t>5.6.2-model-I2C_TX_8mA_tx-5be0a130d535</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5.4.4</t>
+          <t>5.6.2</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LEVEL 2</t>
+          <t>LEVEL 3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -14729,14 +14735,14 @@
           <t>semi_auto</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E58" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -14766,7 +14772,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>V-T endpoint fixture evidence is within threshold</t>
+          <t>Model_type=I/O does not require this Vref consistency evidence</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -14778,12 +14784,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5.5.4-model-I2C_TX_8mA_tx-0eb3274c2b46</t>
+          <t>5.1.2-model-I3C_TX_0p125mA_tx-585be6e97e4c</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5.5.4</t>
+          <t>5.1.2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -14813,7 +14819,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>I2C_TX_8mA_tx</t>
+          <t>I3C_TX_0p125mA_tx</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -14833,29 +14839,29 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Ramp dt evidence is near V-T 20-80% crossing span</t>
+          <t>C_comp evidence is positive and within review threshold</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>avg Ramp dt=1.644e-10s, avg V-T 20-80% span=1.581e-10s, diff=4.0%</t>
+          <t>C_comp</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5.6.2-model-I2C_TX_8mA_tx-3a7350a98cbf</t>
+          <t>5.1.4-model-I3C_TX_0p125mA_tx-73bcf4a8710d</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5.6.2</t>
+          <t>5.1.4</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LEVEL 3</t>
+          <t>LEVEL 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -14863,14 +14869,14 @@
           <t>semi_auto</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+      <c r="E60" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -14880,7 +14886,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>I2C_TX_8mA_tx</t>
+          <t>I3C_TX_0p125mA_tx</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -14900,144 +14906,10 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Model_type=I/O does not require this Vref consistency evidence</t>
+          <t>Voltage/reference evidence parsed, defaults resolved, and basic consistency looks reasonable</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>5.1.2-model-I3C_TX_0p125mA_tx-9a457c8b5815</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>5.1.2</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>semi_auto</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>I3C_TX_0p125mA_tx</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>C_comp evidence is positive and within review threshold</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>C_comp</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>5.1.4-model-I3C_TX_0p125mA_tx-c1fad32f29cf</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>5.1.4</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>semi_auto</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>I3C_TX_0p125mA_tx</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>Voltage/reference evidence parsed, defaults resolved, and basic consistency looks reasonable</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
         <is>
           <t>Voltage Range: typ=1.2V, min=1.08V, max=1.32V (explicit)
 Pullup Reference: typ=1.2V, min=1.08V, max=1.32V (explicit)
@@ -15047,15 +14919,150 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>5.3.6-model-I3C_TX_0p125mA_tx-a7ed0ea8a3af</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5.3.6</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>semi_auto</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr" s="6">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr" s="6">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>I3C_TX_0p125mA_tx</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>I-V stair-step evidence needs review</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>[GND Clamp]: roughness=0.262 &gt; 0.1
+[POWER Clamp]: roughness=0.2 &gt; 0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>5.3.14-model-I3C_TX_0p125mA_tx-18d672fe52aa</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5.3.14</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>semi_auto</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>I3C_TX_0p125mA_tx</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>I-V point counts meet evidence threshold</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5.3.6-model-I3C_TX_0p125mA_tx-17fcb2bc6d07</t>
+          <t>5.3.10-model-I3C_TX_0p125mA_tx-2b7c9b7ef4fc</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5.3.6</t>
+          <t>5.3.10</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -15068,14 +15075,14 @@
           <t>semi_auto</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr" s="6">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr" s="6">
-        <is>
-          <t>WARN</t>
+      <c r="E63" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -15090,7 +15097,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -15105,25 +15112,24 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>I-V stair-step evidence needs review</t>
+          <t>Clamp leakage evidence is within threshold at 0V</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>[GND Clamp]: roughness=0.262 &gt; 0.1
-[POWER Clamp]: roughness=0.2 &gt; 0.1</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5.3.14-model-I3C_TX_0p125mA_tx-70c202487cd4</t>
+          <t>5.4.1-model-I3C_TX_0p125mA_tx-6199dfc8ef85</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5.3.14</t>
+          <t>5.4.1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -15173,7 +15179,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>I-V point counts meet evidence threshold</t>
+          <t>V-T waveform evidence includes 2 rising and 2 falling table(s)</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -15185,12 +15191,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5.3.10-model-I3C_TX_0p125mA_tx-930881fa0a02</t>
+          <t>5.4.2-model-I3C_TX_0p125mA_tx-0f10dddf9621</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5.3.10</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -15240,7 +15246,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Clamp leakage evidence is within threshold at 0V</t>
+          <t>V-T point counts meet evidence threshold</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -15252,17 +15258,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5.4.1-model-I3C_TX_0p125mA_tx-f7e544f48c83</t>
+          <t>5.4.3-model-I3C_TX_0p125mA_tx-48bf36a7a63b</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5.4.1</t>
+          <t>5.4.3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LEVEL 2</t>
+          <t>LEVEL 3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -15307,7 +15313,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>V-T waveform evidence includes 2 rising and 2 falling table(s)</t>
+          <t>V-T duration evidence is within threshold</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -15319,12 +15325,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5.4.2-model-I3C_TX_0p125mA_tx-b6d0a734533e</t>
+          <t>5.4.4-model-I3C_TX_0p125mA_tx-c2e26972b6ae</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>5.4.4</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -15374,7 +15380,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>V-T point counts meet evidence threshold</t>
+          <t>V-T endpoint fixture evidence is within threshold</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -15386,17 +15392,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5.4.3-model-I3C_TX_0p125mA_tx-e8c974c1126f</t>
+          <t>5.5.4-model-I3C_TX_0p125mA_tx-629f7e033922</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5.4.3</t>
+          <t>5.5.4</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LEVEL 3</t>
+          <t>LEVEL 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -15441,29 +15447,29 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>V-T duration evidence is within threshold</t>
+          <t>Ramp dt evidence is near V-T 20-80% crossing span</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t/>
+          <t>avg Ramp dt=1.658e-10s, avg V-T 20-80% span=1.594e-10s, diff=4.0%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5.4.4-model-I3C_TX_0p125mA_tx-8bd60dcf0d9d</t>
+          <t>5.6.2-model-I3C_TX_0p125mA_tx-c56e71c473f8</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5.4.4</t>
+          <t>5.6.2</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LEVEL 2</t>
+          <t>LEVEL 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -15471,14 +15477,14 @@
           <t>semi_auto</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E69" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -15508,7 +15514,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>V-T endpoint fixture evidence is within threshold</t>
+          <t>Model_type=I/O does not require this Vref consistency evidence</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -15520,12 +15526,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5.5.4-model-I3C_TX_0p125mA_tx-86ec84119bd1</t>
+          <t>5.3.1-model-I3C_RX_RPU0RPD0_rx-c05cb6fb188b</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5.5.4</t>
+          <t>5.3.1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -15535,7 +15541,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>semi_auto</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="4">
@@ -15555,7 +15561,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>I3C_TX_0p125mA_tx</t>
+          <t>I3C_RX_RPU0RPD0_rx</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15575,44 +15581,44 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Ramp dt evidence is near V-T 20-80% crossing span</t>
+          <t>[GND Clamp] rows are voltage/typ/min/max</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>avg Ramp dt=1.658e-10s, avg V-T 20-80% span=1.594e-10s, diff=4.0%</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5.6.2-model-I3C_TX_0p125mA_tx-44b8c3888bc7</t>
+          <t>5.3.1-model-I3C_RX_RPU0RPD0_rx-c05cb6fb188b-2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5.6.2</t>
+          <t>5.3.1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LEVEL 3</t>
+          <t>LEVEL 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>semi_auto</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -15622,7 +15628,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>I3C_TX_0p125mA_tx</t>
+          <t>I3C_RX_RPU0RPD0_rx</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15642,7 +15648,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Model_type=I/O does not require this Vref consistency evidence</t>
+          <t>[POWER Clamp] rows are voltage/typ/min/max</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -15654,12 +15660,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5.3.1-model-I3C_RX_RPU0RPD0_rx-2e786608c93b</t>
+          <t>5.3.2-model-I3C_RX_RPU0RPD0_rx-09477b4af9e5</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>5.3.2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -15672,14 +15678,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E72" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -15709,7 +15715,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>[GND Clamp] rows are voltage/typ/min/max</t>
+          <t>Model_type=Input has no required [Pullup] table - NA</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -15721,12 +15727,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5.3.1-model-I3C_RX_RPU0RPD0_rx-c0c8ee78c0c4</t>
+          <t>5.3.3-model-I3C_RX_RPU0RPD0_rx-65c78f72f64f</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>5.3.3</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -15739,14 +15745,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E73" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -15776,7 +15782,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>[POWER Clamp] rows are voltage/typ/min/max</t>
+          <t>Model_type=Input has no required [Pulldown] table - NA</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -15788,12 +15794,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5.3.2-model-I3C_RX_RPU0RPD0_rx-c9c34c61743d</t>
+          <t>5.3.4-model-I3C_RX_RPU0RPD0_rx-0ff765d4d01e</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5.3.2</t>
+          <t>5.3.4</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -15806,14 +15812,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+      <c r="E74" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -15843,7 +15849,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Model_type=Input has no required [Pullup] table - NA</t>
+          <t>[POWER Clamp] voltage sweep OK (-1.2V to 2.4V)</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -15855,12 +15861,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5.3.3-model-I3C_RX_RPU0RPD0_rx-04634d7bf787</t>
+          <t>5.3.5-model-I3C_RX_RPU0RPD0_rx-048d3c9d4a95</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5.3.3</t>
+          <t>5.3.5</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -15873,14 +15879,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+      <c r="E75" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -15910,7 +15916,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Model_type=Input has no required [Pulldown] table - NA</t>
+          <t>[GND Clamp] voltage sweep OK (-1.2V to 2.4V)</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -15922,12 +15928,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5.3.4-model-I3C_RX_RPU0RPD0_rx-b91790150d1c</t>
+          <t>5.3.7-model-I3C_RX_RPU0RPD0_rx-04a28a1c192e</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5.3.4</t>
+          <t>5.3.7</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -15940,14 +15946,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E76" t="inlineStr" s="5">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr" s="5">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -15977,24 +15983,24 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>[POWER Clamp] voltage sweep OK (-1.2V to 2.4V)</t>
+          <t>[Pulldown] + [GND Clamp] combined curve non-monotonic (1 violation(s))</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t/>
+          <t>V=1.238: combined current decreases from 4.698e-06mA to 0mA</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5.3.5-model-I3C_RX_RPU0RPD0_rx-d0e01180152e</t>
+          <t>5.3.7-model-I3C_RX_RPU0RPD0_rx-04a28a1c192e-2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5.3.5</t>
+          <t>5.3.7</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -16044,7 +16050,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>[GND Clamp] voltage sweep OK (-1.2V to 2.4V)</t>
+          <t>[Pullup] + [POWER Clamp] combined curve monotonicity OK (nonincreasing, 83 sample point(s))</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -16056,12 +16062,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5.3.7-model-I3C_RX_RPU0RPD0_rx-44fe45c6e6e0</t>
+          <t>5.3.8-model-I3C_RX_RPU0RPD0_rx-f446cc148eb6</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5.3.7</t>
+          <t>5.3.8</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -16074,14 +16080,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr" s="5">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr" s="5">
-        <is>
-          <t>FAIL</t>
+      <c r="E78" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -16111,24 +16117,24 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>[Pulldown] + [GND Clamp] combined curve non-monotonic (1 violation(s))</t>
+          <t>Model_type=Input has no required [Pulldown] table - NA</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>V=1.238: combined current decreases from 4.698e-06mA to 0mA</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5.3.7-model-I3C_RX_RPU0RPD0_rx-b4821a97fcf5</t>
+          <t>5.3.9-model-I3C_RX_RPU0RPD0_rx-54c65dba6fed</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5.3.7</t>
+          <t>5.3.9</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -16141,14 +16147,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E79" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -16178,7 +16184,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>[Pullup] + [POWER Clamp] combined curve monotonicity OK (nonincreasing, 83 sample point(s))</t>
+          <t>Model_type=Input has no required [Pullup] table - NA</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -16190,12 +16196,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5.3.8-model-I3C_RX_RPU0RPD0_rx-3f61e89fbc70</t>
+          <t>5.3.1-model-I2C_RX_RPU1RPD0_rx-80d4f34b92ec</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5.3.8</t>
+          <t>5.3.1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -16208,14 +16214,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+      <c r="E80" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -16225,7 +16231,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>I3C_RX_RPU0RPD0_rx</t>
+          <t>I2C_RX_RPU1RPD0_rx</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -16245,7 +16251,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Model_type=Input has no required [Pulldown] table - NA</t>
+          <t>[GND Clamp] rows are voltage/typ/min/max</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -16257,12 +16263,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5.3.9-model-I3C_RX_RPU0RPD0_rx-951ed6aeaead</t>
+          <t>5.3.1-model-I2C_RX_RPU1RPD0_rx-80d4f34b92ec-2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5.3.9</t>
+          <t>5.3.1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -16275,14 +16281,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+      <c r="E81" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -16292,7 +16298,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>I3C_RX_RPU0RPD0_rx</t>
+          <t>I2C_RX_RPU1RPD0_rx</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -16312,7 +16318,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Model_type=Input has no required [Pullup] table - NA</t>
+          <t>[POWER Clamp] rows are voltage/typ/min/max</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -16324,12 +16330,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5.3.1-model-I2C_RX_RPU1RPD0_rx-7a12ca646bb7</t>
+          <t>5.3.2-model-I2C_RX_RPU1RPD0_rx-a1ae38861716</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>5.3.2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -16342,14 +16348,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E82" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -16379,7 +16385,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>[GND Clamp] rows are voltage/typ/min/max</t>
+          <t>Model_type=Input has no required [Pullup] table - NA</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -16391,12 +16397,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5.3.1-model-I2C_RX_RPU1RPD0_rx-c429b4481f13</t>
+          <t>5.3.3-model-I2C_RX_RPU1RPD0_rx-41306a512e57</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>5.3.3</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -16409,14 +16415,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E83" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -16446,7 +16452,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>[POWER Clamp] rows are voltage/typ/min/max</t>
+          <t>Model_type=Input has no required [Pulldown] table - NA</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -16458,12 +16464,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5.3.2-model-I2C_RX_RPU1RPD0_rx-7faa94dfc345</t>
+          <t>5.3.4-model-I2C_RX_RPU1RPD0_rx-48a5045fad7d</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5.3.2</t>
+          <t>5.3.4</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -16476,14 +16482,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+      <c r="E84" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -16513,7 +16519,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Model_type=Input has no required [Pullup] table - NA</t>
+          <t>[POWER Clamp] voltage sweep OK (-1.2V to 2.4V)</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -16525,12 +16531,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5.3.3-model-I2C_RX_RPU1RPD0_rx-29b7b990c3f0</t>
+          <t>5.3.5-model-I2C_RX_RPU1RPD0_rx-d18d47a92a16</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5.3.3</t>
+          <t>5.3.5</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -16543,14 +16549,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+      <c r="E85" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -16580,7 +16586,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Model_type=Input has no required [Pulldown] table - NA</t>
+          <t>[GND Clamp] voltage sweep OK (-1.2V to 2.4V)</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -16592,12 +16598,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5.3.4-model-I2C_RX_RPU1RPD0_rx-0e0fe51f3422</t>
+          <t>5.3.7-model-I2C_RX_RPU1RPD0_rx-ad4f414bcdd0</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5.3.4</t>
+          <t>5.3.7</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -16610,14 +16616,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E86" t="inlineStr" s="5">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr" s="5">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -16647,24 +16653,24 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>[POWER Clamp] voltage sweep OK (-1.2V to 2.4V)</t>
+          <t>[Pulldown] + [GND Clamp] combined curve non-monotonic (1 violation(s))</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t/>
+          <t>V=1.238: combined current decreases from 4.695e-06mA to 0mA</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5.3.5-model-I2C_RX_RPU1RPD0_rx-7e9997413e8d</t>
+          <t>5.3.7-model-I2C_RX_RPU1RPD0_rx-ad4f414bcdd0-2</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5.3.5</t>
+          <t>5.3.7</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -16714,7 +16720,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>[GND Clamp] voltage sweep OK (-1.2V to 2.4V)</t>
+          <t>[Pullup] + [POWER Clamp] combined curve monotonicity OK (nonincreasing, 83 sample point(s))</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -16726,12 +16732,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5.3.7-model-I2C_RX_RPU1RPD0_rx-7d77545c79da</t>
+          <t>5.3.8-model-I2C_RX_RPU1RPD0_rx-95f64a2bc18c</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5.3.7</t>
+          <t>5.3.8</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -16744,14 +16750,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr" s="5">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr" s="5">
-        <is>
-          <t>FAIL</t>
+      <c r="E88" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -16781,24 +16787,24 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>[Pulldown] + [GND Clamp] combined curve non-monotonic (1 violation(s))</t>
+          <t>Model_type=Input has no required [Pulldown] table - NA</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>V=1.238: combined current decreases from 4.695e-06mA to 0mA</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5.3.7-model-I2C_RX_RPU1RPD0_rx-a871eb783824</t>
+          <t>5.3.9-model-I2C_RX_RPU1RPD0_rx-0446b0343958</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5.3.7</t>
+          <t>5.3.9</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -16811,14 +16817,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E89" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -16848,7 +16854,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>[Pullup] + [POWER Clamp] combined curve monotonicity OK (nonincreasing, 83 sample point(s))</t>
+          <t>Model_type=Input has no required [Pullup] table - NA</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -16860,12 +16866,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5.3.8-model-I2C_RX_RPU1RPD0_rx-8a3f9a3e9807</t>
+          <t>5.3.1-model-I2C_TX_8mA_tx-b5826245cfb6</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5.3.8</t>
+          <t>5.3.1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -16878,14 +16884,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+      <c r="E90" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -16895,7 +16901,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>I2C_RX_RPU1RPD0_rx</t>
+          <t>I2C_TX_8mA_tx</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -16915,7 +16921,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Model_type=Input has no required [Pulldown] table - NA</t>
+          <t>[Pulldown] rows are voltage/typ/min/max with expected active-region corner ordering</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -16927,12 +16933,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5.3.9-model-I2C_RX_RPU1RPD0_rx-497eba3e6b9f</t>
+          <t>5.3.1-model-I2C_TX_8mA_tx-b5826245cfb6-2</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5.3.9</t>
+          <t>5.3.1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -16945,14 +16951,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr" s="7">
-        <is>
-          <t>NA</t>
+      <c r="E91" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -16962,7 +16968,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>I2C_RX_RPU1RPD0_rx</t>
+          <t>I2C_TX_8mA_tx</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -16982,7 +16988,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Model_type=Input has no required [Pullup] table - NA</t>
+          <t>[Pullup] rows are voltage/typ/min/max with expected active-region corner ordering</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -16994,7 +17000,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5.3.1-model-I2C_TX_8mA_tx-981afc9b1d5d</t>
+          <t>5.3.1-model-I2C_TX_8mA_tx-b5826245cfb6-3</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -17049,7 +17055,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>[Pulldown] rows are voltage/typ/min/max with expected active-region corner ordering</t>
+          <t>[GND Clamp] rows are voltage/typ/min/max</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -17061,7 +17067,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5.3.1-model-I2C_TX_8mA_tx-fbb836090a1c</t>
+          <t>5.3.1-model-I2C_TX_8mA_tx-b5826245cfb6-4</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -17116,7 +17122,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>[Pullup] rows are voltage/typ/min/max with expected active-region corner ordering</t>
+          <t>[POWER Clamp] rows are voltage/typ/min/max</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -17128,12 +17134,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5.3.1-model-I2C_TX_8mA_tx-057302f95130</t>
+          <t>5.3.2-model-I2C_TX_8mA_tx-06b2adef9936</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>5.3.2</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -17183,7 +17189,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>[GND Clamp] rows are voltage/typ/min/max</t>
+          <t>[Pullup] voltage sweep OK (-1.2V to 2.4V)</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -17195,12 +17201,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5.3.1-model-I2C_TX_8mA_tx-4e744d83a50c</t>
+          <t>5.3.3-model-I2C_TX_8mA_tx-24a6b115e097</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>5.3.3</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -17250,7 +17256,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>[POWER Clamp] rows are voltage/typ/min/max</t>
+          <t>[Pulldown] voltage sweep OK (-1.2V to 2.4V)</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -17262,12 +17268,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5.3.2-model-I2C_TX_8mA_tx-bd2cc9a7e595</t>
+          <t>5.3.4-model-I2C_TX_8mA_tx-ae51993d28b7</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5.3.2</t>
+          <t>5.3.4</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -17317,7 +17323,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>[Pullup] voltage sweep OK (-1.2V to 2.4V)</t>
+          <t>[POWER Clamp] voltage sweep OK (-1.2V to 2.4V)</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -17329,12 +17335,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5.3.3-model-I2C_TX_8mA_tx-391f16d5a008</t>
+          <t>5.3.5-model-I2C_TX_8mA_tx-c4b8aea5f685</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5.3.3</t>
+          <t>5.3.5</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -17384,7 +17390,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>[Pulldown] voltage sweep OK (-1.2V to 2.4V)</t>
+          <t>[GND Clamp] voltage sweep OK (-1.2V to 2.4V)</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -17396,12 +17402,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5.3.4-model-I2C_TX_8mA_tx-2d3372af1b6e</t>
+          <t>5.3.7-model-I2C_TX_8mA_tx-e439a321e418</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5.3.4</t>
+          <t>5.3.7</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -17414,14 +17420,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E98" t="inlineStr" s="5">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr" s="5">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -17451,144 +17457,10 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>[POWER Clamp] voltage sweep OK (-1.2V to 2.4V)</t>
+          <t>[Pulldown] + [GND Clamp] combined curve non-monotonic (18 violation(s))</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>5.3.5-model-I2C_TX_8mA_tx-2f3c4b45245f</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>5.3.5</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>I2C_TX_8mA_tx</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>[GND Clamp] voltage sweep OK (-1.2V to 2.4V)</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>5.3.7-model-I2C_TX_8mA_tx-10bba47fb3ee</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>5.3.7</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr" s="5">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr" s="5">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>I2C_TX_8mA_tx</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>[Pulldown] + [GND Clamp] combined curve non-monotonic (18 violation(s))</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
         <is>
           <t>V=1.725: combined current decreases from 43.22mA to 43.1mA
 V=1.762: combined current decreases from 43.1mA to 42.84mA
@@ -17603,68 +17475,68 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>5.3.7-model-I2C_TX_8mA_tx-89f0999b49a2</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>5.3.7-model-I2C_TX_8mA_tx-e439a321e418-2</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
         <is>
           <t>5.3.7</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr" s="5">
+      <c r="E99" t="inlineStr" s="5">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr" s="5">
+      <c r="F99" t="inlineStr" s="5">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>I2C_TX_8mA_tx</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
+      <c r="J99" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t>[Pullup] + [POWER Clamp] combined curve non-monotonic (19 violation(s))</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>V=1.688: combined current increases from -43.91mA to -43.9mA
 V=1.725: combined current increases from -43.9mA to -43.75mA
@@ -17679,15 +17551,149 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>5.3.8-model-I2C_TX_8mA_tx-7008511b6615</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>5.3.8</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>I2C_TX_8mA_tx</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>[Pulldown] passes through near 0 at 0V (within +/-1uA)</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>5.3.9-model-I2C_TX_8mA_tx-e76c421c317b</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5.3.9</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>I2C_TX_8mA_tx</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>[Pullup] passes through near 0 at 0V (within +/-1uA)</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5.3.8-model-I2C_TX_8mA_tx-376377c85328</t>
+          <t>5.3.1-model-I3C_TX_0p125mA_tx-4114e9798c5d</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5.3.8</t>
+          <t>5.3.1</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -17717,7 +17723,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>I2C_TX_8mA_tx</t>
+          <t>I3C_TX_0p125mA_tx</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -17737,7 +17743,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>[Pulldown] passes through near 0 at 0V (within +/-1uA)</t>
+          <t>[Pulldown] rows are voltage/typ/min/max with expected active-region corner ordering</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -17749,12 +17755,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5.3.9-model-I2C_TX_8mA_tx-c0942d292009</t>
+          <t>5.3.1-model-I3C_TX_0p125mA_tx-4114e9798c5d-2</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5.3.9</t>
+          <t>5.3.1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -17784,7 +17790,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>I2C_TX_8mA_tx</t>
+          <t>I3C_TX_0p125mA_tx</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -17804,7 +17810,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>[Pullup] passes through near 0 at 0V (within +/-1uA)</t>
+          <t>[Pullup] rows are voltage/typ/min/max with expected active-region corner ordering</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -17816,7 +17822,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5.3.1-model-I3C_TX_0p125mA_tx-daa662b1e8e6</t>
+          <t>5.3.1-model-I3C_TX_0p125mA_tx-4114e9798c5d-3</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -17871,7 +17877,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>[Pulldown] rows are voltage/typ/min/max with expected active-region corner ordering</t>
+          <t>[GND Clamp] rows are voltage/typ/min/max</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -17883,7 +17889,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5.3.1-model-I3C_TX_0p125mA_tx-979d8890c21e</t>
+          <t>5.3.1-model-I3C_TX_0p125mA_tx-4114e9798c5d-4</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -17938,7 +17944,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>[Pullup] rows are voltage/typ/min/max with expected active-region corner ordering</t>
+          <t>[POWER Clamp] rows are voltage/typ/min/max</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -17950,12 +17956,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5.3.1-model-I3C_TX_0p125mA_tx-50172bb102bd</t>
+          <t>5.3.2-model-I3C_TX_0p125mA_tx-197f05e8550a</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>5.3.2</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -18005,7 +18011,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>[GND Clamp] rows are voltage/typ/min/max</t>
+          <t>[Pullup] voltage sweep OK (-1.2V to 2.4V)</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -18017,12 +18023,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5.3.1-model-I3C_TX_0p125mA_tx-f4be4ac53f11</t>
+          <t>5.3.3-model-I3C_TX_0p125mA_tx-b5a8de20b07e</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>5.3.3</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -18072,7 +18078,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>[POWER Clamp] rows are voltage/typ/min/max</t>
+          <t>[Pulldown] voltage sweep OK (-1.2V to 2.4V)</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -18084,12 +18090,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5.3.2-model-I3C_TX_0p125mA_tx-f1f6b2a23735</t>
+          <t>5.3.4-model-I3C_TX_0p125mA_tx-5817362bc7ce</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5.3.2</t>
+          <t>5.3.4</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -18139,7 +18145,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>[Pullup] voltage sweep OK (-1.2V to 2.4V)</t>
+          <t>[POWER Clamp] voltage sweep OK (-1.2V to 2.4V)</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -18151,12 +18157,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5.3.3-model-I3C_TX_0p125mA_tx-d1b0d5fdca95</t>
+          <t>5.3.5-model-I3C_TX_0p125mA_tx-6afc9dd7ab97</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5.3.3</t>
+          <t>5.3.5</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -18206,7 +18212,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>[Pulldown] voltage sweep OK (-1.2V to 2.4V)</t>
+          <t>[GND Clamp] voltage sweep OK (-1.2V to 2.4V)</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -18218,12 +18224,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5.3.4-model-I3C_TX_0p125mA_tx-6320d94838a2</t>
+          <t>5.3.7-model-I3C_TX_0p125mA_tx-df58baf9930c</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5.3.4</t>
+          <t>5.3.7</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -18236,14 +18242,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E110" t="inlineStr" s="5">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr" s="5">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -18273,144 +18279,10 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>[POWER Clamp] voltage sweep OK (-1.2V to 2.4V)</t>
+          <t>[Pulldown] + [GND Clamp] combined curve non-monotonic (17 violation(s))</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>5.3.5-model-I3C_TX_0p125mA_tx-17c5d0ad7daa</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>5.3.5</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>I3C_TX_0p125mA_tx</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>[GND Clamp] voltage sweep OK (-1.2V to 2.4V)</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>5.3.7-model-I3C_TX_0p125mA_tx-d97673ee0289</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>5.3.7</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr" s="5">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr" s="5">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>I3C_TX_0p125mA_tx</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>[Pulldown] + [GND Clamp] combined curve non-monotonic (17 violation(s))</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
         <is>
           <t>V=1.762: combined current decreases from 1.128mA to 1.125mA
 V=1.8: combined current decreases from 1.125mA to 1.118mA
@@ -18425,68 +18297,68 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>5.3.7-model-I3C_TX_0p125mA_tx-38cafd1d65e9</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>5.3.7-model-I3C_TX_0p125mA_tx-df58baf9930c-2</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
         <is>
           <t>5.3.7</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr" s="5">
+      <c r="E111" t="inlineStr" s="5">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr" s="5">
+      <c r="F111" t="inlineStr" s="5">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="H111" t="inlineStr">
         <is>
           <t>I3C_TX_0p125mA_tx</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
+      <c r="J111" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
         <is>
           <t>[Pullup] + [POWER Clamp] combined curve non-monotonic (16 violation(s))</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t>V=1.8: combined current increases from -1.176mA to -1.174mA
 V=1.837: combined current increases from -1.174mA to -1.17mA
@@ -18501,15 +18373,149 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>5.3.8-model-I3C_TX_0p125mA_tx-4d18f1dc8368</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>5.3.8</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>I3C_TX_0p125mA_tx</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>[Pulldown] passes through near 0 at 0V (within +/-1uA)</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>5.3.9-model-I3C_TX_0p125mA_tx-34e3e84d29ea</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>5.3.9</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>I3C_TX_0p125mA_tx</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>[Pullup] passes through near 0 at 0V (within +/-1uA)</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5.3.8-model-I3C_TX_0p125mA_tx-77e6b1df8aea</t>
+          <t>5.5.1-model-I2C_TX_8mA_tx-bb179e3dbff0</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5.3.8</t>
+          <t>5.5.1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -18539,7 +18545,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>I3C_TX_0p125mA_tx</t>
+          <t>I2C_TX_8mA_tx</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -18559,7 +18565,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>[Pulldown] passes through near 0 at 0V (within +/-1uA)</t>
+          <t>R_load = 50.0Ω documented</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -18571,12 +18577,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5.3.9-model-I3C_TX_0p125mA_tx-baa2537d75dd</t>
+          <t>5.5.3-model-I2C_TX_8mA_tx-dffd81f60a43</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5.3.9</t>
+          <t>5.5.3</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -18589,14 +18595,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E115" t="inlineStr" s="5">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr" s="5">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -18606,7 +18612,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>I3C_TX_0p125mA_tx</t>
+          <t>I2C_TX_8mA_tx</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -18626,144 +18632,10 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>[Pullup] passes through near 0 at 0V (within +/-1uA)</t>
+          <t>[Ramp] dV inconsistent with I-V load-line (2 corner(s))</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>5.5.1-model-I2C_TX_8mA_tx-56019e9b413f</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>5.5.1</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>I2C_TX_8mA_tx</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>R_load = 50.0Ω documented</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>5.5.3-model-I2C_TX_8mA_tx-4079f2348f8a</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>5.5.3</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr" s="5">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr" s="5">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>I2C_TX_8mA_tx</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>[Ramp] dV inconsistent with I-V load-line (2 corner(s))</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
         <is>
           <t>Rise dV/max: ramp=0.5045V, expected≈0.4584V (10.0% error, limit 10.0%)
 Fall dV/max: ramp=0.5017V, expected≈0.4559V (10.0% error, limit 10.0%)
@@ -18776,135 +18648,135 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>5.5.1-model-I3C_TX_0p125mA_tx-1fea51e9fa97</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>5.5.1-model-I3C_TX_0p125mA_tx-1d98baec8c87</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
         <is>
           <t>5.5.1</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr" s="4">
+      <c r="E116" t="inlineStr" s="4">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr" s="4">
+      <c r="F116" t="inlineStr" s="4">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="H116" t="inlineStr">
         <is>
           <t>I3C_TX_0p125mA_tx</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="I116" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
+      <c r="J116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
         <is>
           <t>R_load = 50.0Ω documented</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>5.5.3-model-I3C_TX_0p125mA_tx-32e78c718020</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
+      <c r="M116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>5.5.3-model-I3C_TX_0p125mA_tx-f03e93317e49</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
         <is>
           <t>5.5.3</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>LEVEL 2</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr" s="5">
+      <c r="E117" t="inlineStr" s="5">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr" s="5">
+      <c r="F117" t="inlineStr" s="5">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>I3C_TX_0p125mA_tx</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
+      <c r="J117" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
         <is>
           <t>[Ramp] dV inconsistent with I-V load-line (2 corner(s))</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t>Rise dV/max: ramp=0.03503V, expected≈0.03171V (10.5% error, limit 10.0%)
 Fall dV/max: ramp=0.03401V, expected≈0.03081V (10.4% error, limit 10.0%)
@@ -18917,6 +18789,279 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>5.9.1-model-I3C_RX_RPU0RPD0_rx-86c3e558f8ae</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>5.9.1</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>I3C_RX_RPU0RPD0_rx</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Model_type=Input has no Pullup/Pulldown — Zout NA</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>5.9.1-model-I2C_RX_RPU1RPD0_rx-57ba5f6590ba</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>5.9.1</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>I2C_RX_RPU1RPD0_rx</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Model_type=Input has no Pullup/Pulldown — Zout NA</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>5.9.1-model-I2C_TX_8mA_tx-8e65e8e81d5b</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>5.9.1</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>I2C_TX_8mA_tx</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Zout worst-case 45.6Ω within 100Ω threshold</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>5.9.1-model-I3C_TX_0p125mA_tx-265dd7d8d945</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>5.9.1</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr" s="6">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr" s="6">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>I3C_TX_0p125mA_tx</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Zout worst-case 1904.2Ω exceeds 100Ω (pulldown min, Rload=50Ω)</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>pulldown min: 1904.2Ω
+pullup min: 1746.7Ω
+pulldown typ: 1394.2Ω
+pullup typ: 1343.6Ω
+pulldown max: 1114.5Ω
+pullup max: 1080.4Ω</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/reports/ibis_files/hibiki/hibiki.xlsx
+++ b/reports/ibis_files/hibiki/hibiki.xlsx
@@ -117,7 +117,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-12T22:46:21-05:00</t>
+          <t>2026-06-13T23:04:08-05:00</t>
         </is>
       </c>
     </row>
